--- a/artfynd/A 42355-2025 artfynd.xlsx
+++ b/artfynd/A 42355-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136870194</v>
       </c>
       <c r="B2" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42355-2025 artfynd.xlsx
+++ b/artfynd/A 42355-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136870194</v>
       </c>
       <c r="B2" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42355-2025 artfynd.xlsx
+++ b/artfynd/A 42355-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136870194</v>
       </c>
       <c r="B2" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42355-2025 artfynd.xlsx
+++ b/artfynd/A 42355-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136870194</v>
       </c>
       <c r="B2" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42355-2025 artfynd.xlsx
+++ b/artfynd/A 42355-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136870194</v>
       </c>
       <c r="B2" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42355-2025 artfynd.xlsx
+++ b/artfynd/A 42355-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136870194</v>
       </c>
       <c r="B2" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42355-2025 artfynd.xlsx
+++ b/artfynd/A 42355-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136870194</v>
       </c>
       <c r="B2" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42355-2025 artfynd.xlsx
+++ b/artfynd/A 42355-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136870194</v>
       </c>
       <c r="B2" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42355-2025 artfynd.xlsx
+++ b/artfynd/A 42355-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136870194</v>
       </c>
       <c r="B2" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42355-2025 artfynd.xlsx
+++ b/artfynd/A 42355-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136870194</v>
       </c>
       <c r="B2" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42355-2025 artfynd.xlsx
+++ b/artfynd/A 42355-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136870194</v>
       </c>
       <c r="B2" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42355-2025 artfynd.xlsx
+++ b/artfynd/A 42355-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136870194</v>
       </c>
       <c r="B2" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42355-2025 artfynd.xlsx
+++ b/artfynd/A 42355-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136870194</v>
       </c>
       <c r="B2" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42355-2025 artfynd.xlsx
+++ b/artfynd/A 42355-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136870194</v>
       </c>
       <c r="B2" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42355-2025 artfynd.xlsx
+++ b/artfynd/A 42355-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136870194</v>
       </c>
       <c r="B2" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42355-2025 artfynd.xlsx
+++ b/artfynd/A 42355-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,38 +680,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136870194</v>
+        <v>136870219</v>
       </c>
       <c r="B2" t="n">
-        <v>99418</v>
+        <v>93475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578444</v>
+        <v>578459</v>
       </c>
       <c r="R2" t="n">
-        <v>6859294</v>
+        <v>6859273</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,6 +779,113 @@
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136870219</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136870194</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99430</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>N Hedåssjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>578444</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6859294</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Delsbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136870194</t>
         </is>
@@ -788,6 +894,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42355-2025 artfynd.xlsx
+++ b/artfynd/A 42355-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136870219</v>
       </c>
       <c r="B2" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136870194</v>
       </c>
       <c r="B3" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42355-2025 artfynd.xlsx
+++ b/artfynd/A 42355-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136870219</v>
       </c>
       <c r="B2" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42355-2025 artfynd.xlsx
+++ b/artfynd/A 42355-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136870219</v>
       </c>
       <c r="B2" t="n">
-        <v>93479</v>
+        <v>93483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
